--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
@@ -413,959 +413,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="C1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Measured by operator 7 on tool HRM-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Max Stepheight</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Min Stepheight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Mean Stepheight</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>18.00841</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.39733</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17.39455</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.87745</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.05423</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.9509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.05593</v>
+        <v>17.90824</v>
       </c>
       <c r="D3" t="n">
-        <v>17.36791</v>
+        <v>17.50528</v>
       </c>
       <c r="E3" t="n">
-        <v>17.68282</v>
+        <v>17.73443</v>
       </c>
       <c r="F3" t="n">
-        <v>45.7562</v>
+        <v>44.21192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05382</v>
+        <v>0.0521</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97548</v>
+        <v>1.88693</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.79228</v>
+        <v>17.79245</v>
       </c>
       <c r="D4" t="n">
-        <v>17.6747</v>
+        <v>17.54869</v>
       </c>
       <c r="E4" t="n">
-        <v>17.66092</v>
+        <v>17.633</v>
       </c>
       <c r="F4" t="n">
-        <v>45.30599</v>
+        <v>45.26695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05446</v>
+        <v>0.05482</v>
       </c>
       <c r="H4" t="n">
-        <v>1.95849</v>
+        <v>1.89658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.721</v>
+        <v>17.77204</v>
       </c>
       <c r="D5" t="n">
-        <v>17.34988</v>
+        <v>17.50472</v>
       </c>
       <c r="E5" t="n">
-        <v>17.66404</v>
+        <v>17.61217</v>
       </c>
       <c r="F5" t="n">
-        <v>44.92566</v>
+        <v>45.64513</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05408</v>
+        <v>0.05353</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91628</v>
+        <v>1.97013</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.93995</v>
+        <v>18.08944</v>
       </c>
       <c r="D6" t="n">
-        <v>17.35074</v>
+        <v>17.33104</v>
       </c>
       <c r="E6" t="n">
-        <v>17.65012</v>
+        <v>17.60069</v>
       </c>
       <c r="F6" t="n">
-        <v>44.33141</v>
+        <v>44.72553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05192</v>
+        <v>0.05226</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91041</v>
+        <v>1.94786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.91049</v>
+        <v>17.81789</v>
       </c>
       <c r="D7" t="n">
-        <v>17.5998</v>
+        <v>17.32788</v>
       </c>
       <c r="E7" t="n">
-        <v>18.03615</v>
+        <v>17.78763</v>
       </c>
       <c r="F7" t="n">
-        <v>45.16874</v>
+        <v>45.35749</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05386</v>
+        <v>0.05456</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92538</v>
+        <v>1.94334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.33178</v>
+        <v>18.02526</v>
       </c>
       <c r="D8" t="n">
-        <v>17.42648</v>
+        <v>17.44819</v>
       </c>
       <c r="E8" t="n">
-        <v>17.57148</v>
+        <v>17.62184</v>
       </c>
       <c r="F8" t="n">
-        <v>45.85388</v>
+        <v>45.5331</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05341</v>
+        <v>0.05372</v>
       </c>
       <c r="H8" t="n">
-        <v>1.89326</v>
+        <v>1.91929</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.45802</v>
+        <v>17.95909</v>
       </c>
       <c r="D9" t="n">
-        <v>17.77502</v>
+        <v>17.90907</v>
       </c>
       <c r="E9" t="n">
-        <v>17.40897</v>
+        <v>17.95893</v>
       </c>
       <c r="F9" t="n">
-        <v>44.79008</v>
+        <v>45.43437</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05422</v>
+        <v>0.05386</v>
       </c>
       <c r="H9" t="n">
-        <v>1.97755</v>
+        <v>1.93851</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.7605</v>
+        <v>17.87401</v>
       </c>
       <c r="D10" t="n">
-        <v>17.92666</v>
+        <v>17.58108</v>
       </c>
       <c r="E10" t="n">
-        <v>17.5372</v>
+        <v>17.62794</v>
       </c>
       <c r="F10" t="n">
-        <v>45.40683</v>
+        <v>44.76647</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05403</v>
+        <v>0.05389</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9558</v>
+        <v>1.95903</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.79587</v>
+        <v>18.15376</v>
       </c>
       <c r="D11" t="n">
-        <v>17.83885</v>
+        <v>17.70283</v>
       </c>
       <c r="E11" t="n">
-        <v>17.3673</v>
+        <v>17.74689</v>
       </c>
       <c r="F11" t="n">
-        <v>45.12068</v>
+        <v>46.01182</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05343</v>
+        <v>0.05423</v>
       </c>
       <c r="H11" t="n">
-        <v>1.92646</v>
+        <v>1.94761</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>17.63372</v>
-      </c>
-      <c r="D12" t="n">
-        <v>17.55233</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.69945</v>
-      </c>
-      <c r="F12" t="n">
-        <v>44.97165</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05219</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.91899</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.99835</v>
+        <v>0.6518699999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>17.52457</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.83322</v>
-      </c>
-      <c r="F13" t="n">
-        <v>44.25129</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05301</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.89993</v>
+        <v>1.15559</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.47471</v>
+        <v>0.64995</v>
       </c>
       <c r="D14" t="n">
-        <v>17.94987</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.56115</v>
-      </c>
-      <c r="F14" t="n">
-        <v>44.2999</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05369</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.94524</v>
+        <v>1.20372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.91625</v>
+        <v>0.63874</v>
       </c>
       <c r="D15" t="n">
-        <v>17.48435</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.62345</v>
-      </c>
-      <c r="F15" t="n">
-        <v>45.72332</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05223</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.89501</v>
+        <v>1.18807</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.82191</v>
+        <v>0.6328</v>
       </c>
       <c r="D16" t="n">
-        <v>17.30214</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.5696</v>
-      </c>
-      <c r="F16" t="n">
-        <v>45.0337</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05225</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.97633</v>
+        <v>1.19105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.89471</v>
+        <v>0.6412</v>
       </c>
       <c r="D17" t="n">
-        <v>17.35771</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.50696</v>
-      </c>
-      <c r="F17" t="n">
-        <v>45.00905</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05209</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.95801</v>
+        <v>1.19739</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.91759</v>
+        <v>0.64896</v>
       </c>
       <c r="D18" t="n">
-        <v>17.48982</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.55468</v>
-      </c>
-      <c r="F18" t="n">
-        <v>45.04557</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05283</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.94039</v>
+        <v>1.18007</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.27024</v>
+        <v>0.64933</v>
       </c>
       <c r="D19" t="n">
-        <v>17.5453</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.57839</v>
-      </c>
-      <c r="F19" t="n">
-        <v>44.7606</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05378</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.92187</v>
+        <v>1.17806</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.65506</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.17084</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6393</v>
+        <v>0.63723</v>
       </c>
       <c r="D21" t="n">
-        <v>1.15285</v>
+        <v>1.17428</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.63436</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.17185</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.64188</v>
+        <v>0.7961</v>
       </c>
       <c r="D23" t="n">
-        <v>1.18807</v>
+        <v>0.08701</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.62936</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.02331</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.11606</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09818</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.13246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.64705</v>
+        <v>0.79369</v>
       </c>
       <c r="D24" t="n">
-        <v>1.15234</v>
+        <v>0.08638999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6326000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.02342</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.11677</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09773</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.13329</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.65156</v>
+        <v>0.79318</v>
       </c>
       <c r="D25" t="n">
-        <v>1.16002</v>
+        <v>0.08511000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6382100000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.02681</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.11576</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09807</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.13427</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.64697</v>
+        <v>0.79437</v>
       </c>
       <c r="D26" t="n">
-        <v>1.17845</v>
+        <v>0.08766</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6524799999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.01053</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.11474</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09796000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.13304</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.62516</v>
+        <v>0.7843</v>
       </c>
       <c r="D27" t="n">
-        <v>1.17431</v>
+        <v>0.0866</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.64353</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.01076</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1159</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.09732</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.13239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6463100000000001</v>
+        <v>0.80358</v>
       </c>
       <c r="D28" t="n">
-        <v>1.17343</v>
+        <v>0.0848</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.64246</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.04579</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09703000000000001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.13268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.64507</v>
+        <v>0.77503</v>
       </c>
       <c r="D29" t="n">
-        <v>1.15096</v>
+        <v>0.08606</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.64383</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.01618</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.11653</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00796</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09701</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.13233</v>
       </c>
     </row>
     <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.80064</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08681</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.63396</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.01518</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.11569</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.008149999999999999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09844</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.79425</v>
+        <v>0.7916</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08469</v>
+        <v>0.08620999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>0.63633</v>
+        <v>0.64962</v>
       </c>
       <c r="F31" t="n">
-        <v>1.01968</v>
+        <v>0.99962</v>
       </c>
       <c r="G31" t="n">
-        <v>0.11627</v>
+        <v>0.11699</v>
       </c>
       <c r="H31" t="n">
-        <v>0.008059999999999999</v>
+        <v>0.00808</v>
       </c>
       <c r="I31" t="n">
-        <v>0.10038</v>
+        <v>0.09830999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.13289</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.78143</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.08434</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.65321</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.03893</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.11684</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.008070000000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0969</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.13402</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.78317</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.08617</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.64473</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.0247</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.11697</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00808</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09941999999999999</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.1328</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.79245</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.08708</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.64988</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.02227</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.11722</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00809</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09701</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.13521</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.78555</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.08578</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.64205</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.01543</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.11628</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.007860000000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09710000000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.13238</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.81044</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.08321000000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.64009</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.9993</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.11423</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00817</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09654</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.13102</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.78412</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.08588999999999999</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.63488</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.02294</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.11738</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00813</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09795</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.13477</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.79508</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.08494</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.6281600000000001</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.02531</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.11546</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.008059999999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09896000000000001</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.133</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.78801</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.08672000000000001</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.64846</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.0276</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.11737</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.10101</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.135</v>
+        <v>0.13389</v>
       </c>
     </row>
   </sheetData>
